--- a/dev_Python/1. 업무/1. 실내공기질/2. 출장지 관리 지도/1. Claude/map_data.xlsx
+++ b/dev_Python/1. 업무/1. 실내공기질/2. 출장지 관리 지도/1. Claude/map_data.xlsx
@@ -1588,7 +1588,11 @@
       <c r="G36" t="n">
         <v>127.0965105</v>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
